--- a/香港現在上映電影 2025-05-30.xlsx
+++ b/香港現在上映電影 2025-05-30.xlsx
@@ -268,7 +268,7 @@
     <t>2.380億</t>
   </si>
   <si>
-    <t>27.35萬</t>
+    <t>27.36萬</t>
   </si>
   <si>
     <t>2.191億</t>
@@ -277,13 +277,13 @@
     <t>3.299億</t>
   </si>
   <si>
-    <t>155.1億</t>
+    <t>155億</t>
   </si>
   <si>
     <t>14.97億</t>
   </si>
   <si>
-    <t>28.09億</t>
+    <t>28.10億</t>
   </si>
   <si>
     <t>17.43億</t>
@@ -301,7 +301,7 @@
     <t>3.934億</t>
   </si>
   <si>
-    <t>7953萬</t>
+    <t>7954萬</t>
   </si>
   <si>
     <t>100</t>
@@ -1084,7 +1084,7 @@
         <v>101</v>
       </c>
       <c r="G10" s="1">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>77</v>
@@ -1113,7 +1113,7 @@
         <v>102</v>
       </c>
       <c r="G11" s="1">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="H11" s="1">
         <v>89</v>
@@ -1183,7 +1183,7 @@
         <v>104</v>
       </c>
       <c r="G13" s="1">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>79</v>
@@ -1212,7 +1212,7 @@
         <v>105</v>
       </c>
       <c r="G14" s="1">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H14" s="1">
         <v>93</v>
